--- a/Outcome/Appendix/Tables/Threshold_sensitivity_analysis.xlsx
+++ b/Outcome/Appendix/Tables/Threshold_sensitivity_analysis.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
   <si>
     <t xml:space="preserve">Config</t>
   </si>
@@ -156,6 +156,15 @@
   </si>
   <si>
     <t xml:space="preserve">95% / 4 mo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100% / 2 mo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100% / 3 mo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100% / 4 mo</t>
   </si>
 </sst>
 </file>
@@ -545,13 +554,13 @@
         <v>44866</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>45689</v>
+        <v>45658</v>
       </c>
       <c r="I2" t="n">
         <v>34</v>
       </c>
       <c r="J2" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3">
@@ -574,11 +583,11 @@
         <v>15</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>45139</v>
+        <v>45170</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J3"/>
     </row>
@@ -630,11 +639,11 @@
         <v>15</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>45597</v>
+        <v>45901</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="J5"/>
     </row>
@@ -762,16 +771,16 @@
         <v>13</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>44805</v>
+        <v>45352</v>
       </c>
       <c r="I10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J10" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11">
@@ -794,16 +803,16 @@
         <v>13</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44682</v>
+        <v>44166</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>44835</v>
+        <v>44805</v>
       </c>
       <c r="I11" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="J11" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12">
@@ -829,13 +838,13 @@
         <v>44682</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>45078</v>
+        <v>44927</v>
       </c>
       <c r="I12" t="n">
         <v>28</v>
       </c>
       <c r="J12" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
@@ -861,13 +870,13 @@
         <v>43983</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>44013</v>
+        <v>44044</v>
       </c>
       <c r="I13" t="n">
         <v>5</v>
       </c>
       <c r="J13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -922,16 +931,16 @@
         <v>13</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44713</v>
+        <v>44774</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>44927</v>
+        <v>45017</v>
       </c>
       <c r="I15" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J15" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16">
@@ -1045,13 +1054,13 @@
         <v>44927</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>45689</v>
+        <v>45597</v>
       </c>
       <c r="I19" t="n">
         <v>36</v>
       </c>
       <c r="J19" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -1071,12 +1080,20 @@
         <v>36</v>
       </c>
       <c r="F20" t="s">
-        <v>20</v>
-      </c>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20"/>
-      <c r="J20"/>
+        <v>13</v>
+      </c>
+      <c r="G20" s="1" t="n">
+        <v>44774</v>
+      </c>
+      <c r="H20" s="1" t="n">
+        <v>45474</v>
+      </c>
+      <c r="I20" t="n">
+        <v>31</v>
+      </c>
+      <c r="J20" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
@@ -1130,13 +1147,13 @@
         <v>13</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45139</v>
+        <v>45108</v>
       </c>
       <c r="H22" s="1" t="n">
         <v>45536</v>
       </c>
       <c r="I22" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J22" t="n">
         <v>56</v>
@@ -1165,13 +1182,13 @@
         <v>44927</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>45383</v>
+        <v>45413</v>
       </c>
       <c r="I23" t="n">
         <v>36</v>
       </c>
       <c r="J23" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24">
@@ -1225,13 +1242,13 @@
         <v>44378</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>44866</v>
+        <v>44896</v>
       </c>
       <c r="I25" t="n">
         <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26">
@@ -1257,13 +1274,13 @@
         <v>44866</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>45689</v>
+        <v>45658</v>
       </c>
       <c r="I26" t="n">
         <v>34</v>
       </c>
       <c r="J26" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27">
@@ -1286,11 +1303,11 @@
         <v>15</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45139</v>
+        <v>45170</v>
       </c>
       <c r="H27" s="1"/>
       <c r="I27" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J27"/>
     </row>
@@ -1311,11 +1328,15 @@
         <v>12</v>
       </c>
       <c r="F28" t="s">
-        <v>20</v>
-      </c>
-      <c r="G28" s="1"/>
+        <v>15</v>
+      </c>
+      <c r="G28" s="1" t="n">
+        <v>45839</v>
+      </c>
       <c r="H28" s="1"/>
-      <c r="I28"/>
+      <c r="I28" t="n">
+        <v>66</v>
+      </c>
       <c r="J28"/>
     </row>
     <row r="29">
@@ -1338,11 +1359,11 @@
         <v>15</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45597</v>
+        <v>45901</v>
       </c>
       <c r="H29" s="1"/>
       <c r="I29" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="J29"/>
     </row>
@@ -1470,16 +1491,16 @@
         <v>13</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>44805</v>
+        <v>45352</v>
       </c>
       <c r="I34" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J34" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35">
@@ -1502,16 +1523,16 @@
         <v>13</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44682</v>
+        <v>44166</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>44835</v>
+        <v>44805</v>
       </c>
       <c r="I35" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="J35" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="36">
@@ -1537,13 +1558,13 @@
         <v>44682</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>45078</v>
+        <v>44927</v>
       </c>
       <c r="I36" t="n">
         <v>28</v>
       </c>
       <c r="J36" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="37">
@@ -1569,13 +1590,13 @@
         <v>43983</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>44013</v>
+        <v>44044</v>
       </c>
       <c r="I37" t="n">
         <v>5</v>
       </c>
       <c r="J37" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38">
@@ -1630,16 +1651,16 @@
         <v>13</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44713</v>
+        <v>44774</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>44927</v>
+        <v>45017</v>
       </c>
       <c r="I39" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J39" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="40">
@@ -1722,11 +1743,11 @@
         <v>15</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45231</v>
+        <v>45261</v>
       </c>
       <c r="H42" s="1"/>
       <c r="I42" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J42"/>
     </row>
@@ -1753,13 +1774,13 @@
         <v>44927</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>45689</v>
+        <v>45597</v>
       </c>
       <c r="I43" t="n">
         <v>36</v>
       </c>
       <c r="J43" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="44">
@@ -1779,12 +1800,20 @@
         <v>36</v>
       </c>
       <c r="F44" t="s">
-        <v>20</v>
-      </c>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44"/>
-      <c r="J44"/>
+        <v>13</v>
+      </c>
+      <c r="G44" s="1" t="n">
+        <v>44927</v>
+      </c>
+      <c r="H44" s="1" t="n">
+        <v>45474</v>
+      </c>
+      <c r="I44" t="n">
+        <v>36</v>
+      </c>
+      <c r="J44" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
@@ -1806,13 +1835,13 @@
         <v>13</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45078</v>
+        <v>44986</v>
       </c>
       <c r="H45" s="1" t="n">
         <v>45413</v>
       </c>
       <c r="I45" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="J45" t="n">
         <v>52</v>
@@ -1838,13 +1867,13 @@
         <v>13</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45139</v>
+        <v>45108</v>
       </c>
       <c r="H46" s="1" t="n">
         <v>45536</v>
       </c>
       <c r="I46" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J46" t="n">
         <v>56</v>
@@ -1873,13 +1902,13 @@
         <v>44927</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>45383</v>
+        <v>45413</v>
       </c>
       <c r="I47" t="n">
         <v>36</v>
       </c>
       <c r="J47" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="48">
@@ -1933,13 +1962,13 @@
         <v>44682</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>44866</v>
+        <v>44896</v>
       </c>
       <c r="I49" t="n">
         <v>28</v>
       </c>
       <c r="J49" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="50">
@@ -1965,13 +1994,13 @@
         <v>44866</v>
       </c>
       <c r="H50" s="1" t="n">
-        <v>45689</v>
+        <v>45658</v>
       </c>
       <c r="I50" t="n">
         <v>34</v>
       </c>
       <c r="J50" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="51">
@@ -1994,11 +2023,11 @@
         <v>15</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45139</v>
+        <v>45170</v>
       </c>
       <c r="H51" s="1"/>
       <c r="I51" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J51"/>
     </row>
@@ -2019,11 +2048,15 @@
         <v>12</v>
       </c>
       <c r="F52" t="s">
-        <v>20</v>
-      </c>
-      <c r="G52" s="1"/>
+        <v>15</v>
+      </c>
+      <c r="G52" s="1" t="n">
+        <v>45839</v>
+      </c>
       <c r="H52" s="1"/>
-      <c r="I52"/>
+      <c r="I52" t="n">
+        <v>66</v>
+      </c>
       <c r="J52"/>
     </row>
     <row r="53">
@@ -2046,11 +2079,11 @@
         <v>15</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45597</v>
+        <v>45901</v>
       </c>
       <c r="H53" s="1"/>
       <c r="I53" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="J53"/>
     </row>
@@ -2178,16 +2211,16 @@
         <v>13</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="H58" s="1" t="n">
-        <v>44805</v>
+        <v>45352</v>
       </c>
       <c r="I58" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J58" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
     </row>
     <row r="59">
@@ -2210,16 +2243,16 @@
         <v>13</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>44682</v>
+        <v>44652</v>
       </c>
       <c r="H59" s="1" t="n">
-        <v>44835</v>
+        <v>44805</v>
       </c>
       <c r="I59" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J59" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="60">
@@ -2245,13 +2278,13 @@
         <v>44682</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>45078</v>
+        <v>44927</v>
       </c>
       <c r="I60" t="n">
         <v>28</v>
       </c>
       <c r="J60" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="61">
@@ -2277,13 +2310,13 @@
         <v>43983</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>44013</v>
+        <v>44044</v>
       </c>
       <c r="I61" t="n">
         <v>5</v>
       </c>
       <c r="J61" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62">
@@ -2306,13 +2339,13 @@
         <v>13</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>44743</v>
+        <v>44105</v>
       </c>
       <c r="H62" s="1" t="n">
         <v>44805</v>
       </c>
       <c r="I62" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="J62" t="n">
         <v>32</v>
@@ -2338,16 +2371,16 @@
         <v>13</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>44713</v>
+        <v>44774</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>44927</v>
+        <v>45017</v>
       </c>
       <c r="I63" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J63" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="64">
@@ -2370,11 +2403,11 @@
         <v>15</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45352</v>
+        <v>45839</v>
       </c>
       <c r="H64" s="1"/>
       <c r="I64" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="J64"/>
     </row>
@@ -2430,11 +2463,11 @@
         <v>15</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45231</v>
+        <v>45261</v>
       </c>
       <c r="H66" s="1"/>
       <c r="I66" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J66"/>
     </row>
@@ -2461,13 +2494,13 @@
         <v>44927</v>
       </c>
       <c r="H67" s="1" t="n">
-        <v>45689</v>
+        <v>45597</v>
       </c>
       <c r="I67" t="n">
         <v>36</v>
       </c>
       <c r="J67" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="68">
@@ -2487,12 +2520,20 @@
         <v>36</v>
       </c>
       <c r="F68" t="s">
-        <v>20</v>
-      </c>
-      <c r="G68" s="1"/>
-      <c r="H68" s="1"/>
-      <c r="I68"/>
-      <c r="J68"/>
+        <v>13</v>
+      </c>
+      <c r="G68" s="1" t="n">
+        <v>45200</v>
+      </c>
+      <c r="H68" s="1" t="n">
+        <v>45474</v>
+      </c>
+      <c r="I68" t="n">
+        <v>45</v>
+      </c>
+      <c r="J68" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
@@ -2514,13 +2555,13 @@
         <v>13</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45078</v>
+        <v>44986</v>
       </c>
       <c r="H69" s="1" t="n">
         <v>45413</v>
       </c>
       <c r="I69" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="J69" t="n">
         <v>52</v>
@@ -2546,13 +2587,13 @@
         <v>13</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45139</v>
+        <v>45108</v>
       </c>
       <c r="H70" s="1" t="n">
         <v>45536</v>
       </c>
       <c r="I70" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J70" t="n">
         <v>56</v>
@@ -2581,13 +2622,13 @@
         <v>44927</v>
       </c>
       <c r="H71" s="1" t="n">
-        <v>45383</v>
+        <v>45413</v>
       </c>
       <c r="I71" t="n">
         <v>36</v>
       </c>
       <c r="J71" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="72">
@@ -2641,13 +2682,13 @@
         <v>44682</v>
       </c>
       <c r="H73" s="1" t="n">
-        <v>44866</v>
+        <v>44896</v>
       </c>
       <c r="I73" t="n">
         <v>28</v>
       </c>
       <c r="J73" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="74">
@@ -2673,13 +2714,13 @@
         <v>44866</v>
       </c>
       <c r="H74" s="1" t="n">
-        <v>45689</v>
+        <v>45658</v>
       </c>
       <c r="I74" t="n">
         <v>34</v>
       </c>
       <c r="J74" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="75">
@@ -2702,11 +2743,11 @@
         <v>15</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>45139</v>
+        <v>45170</v>
       </c>
       <c r="H75" s="1"/>
       <c r="I75" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J75"/>
     </row>
@@ -2758,11 +2799,11 @@
         <v>15</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>45597</v>
+        <v>45901</v>
       </c>
       <c r="H77" s="1"/>
       <c r="I77" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="J77"/>
     </row>
@@ -2890,16 +2931,16 @@
         <v>13</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="H82" s="1" t="n">
-        <v>44805</v>
+        <v>45352</v>
       </c>
       <c r="I82" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J82" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
     </row>
     <row r="83">
@@ -2922,16 +2963,16 @@
         <v>13</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>44682</v>
+        <v>44166</v>
       </c>
       <c r="H83" s="1" t="n">
-        <v>44835</v>
+        <v>44805</v>
       </c>
       <c r="I83" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="J83" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="84">
@@ -2957,13 +2998,13 @@
         <v>44682</v>
       </c>
       <c r="H84" s="1" t="n">
-        <v>45078</v>
+        <v>44927</v>
       </c>
       <c r="I84" t="n">
         <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="85">
@@ -2989,13 +3030,13 @@
         <v>43983</v>
       </c>
       <c r="H85" s="1" t="n">
-        <v>44013</v>
+        <v>44044</v>
       </c>
       <c r="I85" t="n">
         <v>5</v>
       </c>
       <c r="J85" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="86">
@@ -3050,16 +3091,16 @@
         <v>13</v>
       </c>
       <c r="G87" s="1" t="n">
-        <v>44713</v>
+        <v>44774</v>
       </c>
       <c r="H87" s="1" t="n">
-        <v>44927</v>
+        <v>45017</v>
       </c>
       <c r="I87" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J87" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="88">
@@ -3173,13 +3214,13 @@
         <v>44927</v>
       </c>
       <c r="H91" s="1" t="n">
-        <v>45689</v>
+        <v>45597</v>
       </c>
       <c r="I91" t="n">
         <v>36</v>
       </c>
       <c r="J91" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="92">
@@ -3199,12 +3240,20 @@
         <v>36</v>
       </c>
       <c r="F92" t="s">
-        <v>20</v>
-      </c>
-      <c r="G92" s="1"/>
-      <c r="H92" s="1"/>
-      <c r="I92"/>
-      <c r="J92"/>
+        <v>13</v>
+      </c>
+      <c r="G92" s="1" t="n">
+        <v>44774</v>
+      </c>
+      <c r="H92" s="1" t="n">
+        <v>45474</v>
+      </c>
+      <c r="I92" t="n">
+        <v>31</v>
+      </c>
+      <c r="J92" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
@@ -3258,13 +3307,13 @@
         <v>13</v>
       </c>
       <c r="G94" s="1" t="n">
-        <v>45139</v>
+        <v>45108</v>
       </c>
       <c r="H94" s="1" t="n">
         <v>45536</v>
       </c>
       <c r="I94" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J94" t="n">
         <v>56</v>
@@ -3293,13 +3342,13 @@
         <v>44927</v>
       </c>
       <c r="H95" s="1" t="n">
-        <v>45383</v>
+        <v>45413</v>
       </c>
       <c r="I95" t="n">
         <v>36</v>
       </c>
       <c r="J95" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="96">
@@ -3353,13 +3402,13 @@
         <v>44378</v>
       </c>
       <c r="H97" s="1" t="n">
-        <v>44866</v>
+        <v>44896</v>
       </c>
       <c r="I97" t="n">
         <v>18</v>
       </c>
       <c r="J97" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="98">
@@ -3385,13 +3434,13 @@
         <v>44866</v>
       </c>
       <c r="H98" s="1" t="n">
-        <v>45689</v>
+        <v>45658</v>
       </c>
       <c r="I98" t="n">
         <v>34</v>
       </c>
       <c r="J98" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="99">
@@ -3414,11 +3463,11 @@
         <v>15</v>
       </c>
       <c r="G99" s="1" t="n">
-        <v>45139</v>
+        <v>45170</v>
       </c>
       <c r="H99" s="1"/>
       <c r="I99" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J99"/>
     </row>
@@ -3439,11 +3488,15 @@
         <v>12</v>
       </c>
       <c r="F100" t="s">
-        <v>20</v>
-      </c>
-      <c r="G100" s="1"/>
+        <v>15</v>
+      </c>
+      <c r="G100" s="1" t="n">
+        <v>45839</v>
+      </c>
       <c r="H100" s="1"/>
-      <c r="I100"/>
+      <c r="I100" t="n">
+        <v>66</v>
+      </c>
       <c r="J100"/>
     </row>
     <row r="101">
@@ -3466,11 +3519,11 @@
         <v>15</v>
       </c>
       <c r="G101" s="1" t="n">
-        <v>45597</v>
+        <v>45901</v>
       </c>
       <c r="H101" s="1"/>
       <c r="I101" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="J101"/>
     </row>
@@ -3598,16 +3651,16 @@
         <v>13</v>
       </c>
       <c r="G106" s="1" t="n">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="H106" s="1" t="n">
-        <v>44805</v>
+        <v>45352</v>
       </c>
       <c r="I106" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J106" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
     </row>
     <row r="107">
@@ -3630,16 +3683,16 @@
         <v>13</v>
       </c>
       <c r="G107" s="1" t="n">
-        <v>44682</v>
+        <v>44166</v>
       </c>
       <c r="H107" s="1" t="n">
-        <v>44835</v>
+        <v>44805</v>
       </c>
       <c r="I107" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="J107" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="108">
@@ -3665,13 +3718,13 @@
         <v>44682</v>
       </c>
       <c r="H108" s="1" t="n">
-        <v>45078</v>
+        <v>44927</v>
       </c>
       <c r="I108" t="n">
         <v>28</v>
       </c>
       <c r="J108" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="109">
@@ -3697,13 +3750,13 @@
         <v>43983</v>
       </c>
       <c r="H109" s="1" t="n">
-        <v>44013</v>
+        <v>44044</v>
       </c>
       <c r="I109" t="n">
         <v>5</v>
       </c>
       <c r="J109" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="110">
@@ -3758,16 +3811,16 @@
         <v>13</v>
       </c>
       <c r="G111" s="1" t="n">
-        <v>44713</v>
+        <v>44774</v>
       </c>
       <c r="H111" s="1" t="n">
-        <v>44927</v>
+        <v>45017</v>
       </c>
       <c r="I111" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J111" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="112">
@@ -3850,11 +3903,11 @@
         <v>15</v>
       </c>
       <c r="G114" s="1" t="n">
-        <v>45231</v>
+        <v>45261</v>
       </c>
       <c r="H114" s="1"/>
       <c r="I114" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J114"/>
     </row>
@@ -3881,13 +3934,13 @@
         <v>44927</v>
       </c>
       <c r="H115" s="1" t="n">
-        <v>45689</v>
+        <v>45597</v>
       </c>
       <c r="I115" t="n">
         <v>36</v>
       </c>
       <c r="J115" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="116">
@@ -3907,12 +3960,20 @@
         <v>36</v>
       </c>
       <c r="F116" t="s">
-        <v>20</v>
-      </c>
-      <c r="G116" s="1"/>
-      <c r="H116" s="1"/>
-      <c r="I116"/>
-      <c r="J116"/>
+        <v>13</v>
+      </c>
+      <c r="G116" s="1" t="n">
+        <v>44927</v>
+      </c>
+      <c r="H116" s="1" t="n">
+        <v>45474</v>
+      </c>
+      <c r="I116" t="n">
+        <v>36</v>
+      </c>
+      <c r="J116" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
@@ -3934,13 +3995,13 @@
         <v>13</v>
       </c>
       <c r="G117" s="1" t="n">
-        <v>45078</v>
+        <v>44986</v>
       </c>
       <c r="H117" s="1" t="n">
         <v>45413</v>
       </c>
       <c r="I117" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="J117" t="n">
         <v>52</v>
@@ -3966,13 +4027,13 @@
         <v>13</v>
       </c>
       <c r="G118" s="1" t="n">
-        <v>45139</v>
+        <v>45108</v>
       </c>
       <c r="H118" s="1" t="n">
         <v>45536</v>
       </c>
       <c r="I118" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J118" t="n">
         <v>56</v>
@@ -4001,13 +4062,13 @@
         <v>44927</v>
       </c>
       <c r="H119" s="1" t="n">
-        <v>45383</v>
+        <v>45413</v>
       </c>
       <c r="I119" t="n">
         <v>36</v>
       </c>
       <c r="J119" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="120">
@@ -4061,13 +4122,13 @@
         <v>44682</v>
       </c>
       <c r="H121" s="1" t="n">
-        <v>44866</v>
+        <v>44896</v>
       </c>
       <c r="I121" t="n">
         <v>28</v>
       </c>
       <c r="J121" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="122">
@@ -4093,13 +4154,13 @@
         <v>44866</v>
       </c>
       <c r="H122" s="1" t="n">
-        <v>45689</v>
+        <v>45658</v>
       </c>
       <c r="I122" t="n">
         <v>34</v>
       </c>
       <c r="J122" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="123">
@@ -4122,11 +4183,11 @@
         <v>15</v>
       </c>
       <c r="G123" s="1" t="n">
-        <v>45139</v>
+        <v>45170</v>
       </c>
       <c r="H123" s="1"/>
       <c r="I123" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J123"/>
     </row>
@@ -4147,11 +4208,15 @@
         <v>12</v>
       </c>
       <c r="F124" t="s">
-        <v>20</v>
-      </c>
-      <c r="G124" s="1"/>
+        <v>15</v>
+      </c>
+      <c r="G124" s="1" t="n">
+        <v>45839</v>
+      </c>
       <c r="H124" s="1"/>
-      <c r="I124"/>
+      <c r="I124" t="n">
+        <v>66</v>
+      </c>
       <c r="J124"/>
     </row>
     <row r="125">
@@ -4174,11 +4239,11 @@
         <v>15</v>
       </c>
       <c r="G125" s="1" t="n">
-        <v>45597</v>
+        <v>45901</v>
       </c>
       <c r="H125" s="1"/>
       <c r="I125" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="J125"/>
     </row>
@@ -4306,16 +4371,16 @@
         <v>13</v>
       </c>
       <c r="G130" s="1" t="n">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="H130" s="1" t="n">
-        <v>44805</v>
+        <v>45352</v>
       </c>
       <c r="I130" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J130" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
     </row>
     <row r="131">
@@ -4338,16 +4403,16 @@
         <v>13</v>
       </c>
       <c r="G131" s="1" t="n">
-        <v>44682</v>
+        <v>44652</v>
       </c>
       <c r="H131" s="1" t="n">
-        <v>44835</v>
+        <v>44805</v>
       </c>
       <c r="I131" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J131" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="132">
@@ -4373,13 +4438,13 @@
         <v>44682</v>
       </c>
       <c r="H132" s="1" t="n">
-        <v>45078</v>
+        <v>44927</v>
       </c>
       <c r="I132" t="n">
         <v>28</v>
       </c>
       <c r="J132" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="133">
@@ -4405,13 +4470,13 @@
         <v>43983</v>
       </c>
       <c r="H133" s="1" t="n">
-        <v>44013</v>
+        <v>44044</v>
       </c>
       <c r="I133" t="n">
         <v>5</v>
       </c>
       <c r="J133" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="134">
@@ -4434,13 +4499,13 @@
         <v>13</v>
       </c>
       <c r="G134" s="1" t="n">
-        <v>44743</v>
+        <v>44105</v>
       </c>
       <c r="H134" s="1" t="n">
         <v>44805</v>
       </c>
       <c r="I134" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="J134" t="n">
         <v>32</v>
@@ -4466,16 +4531,16 @@
         <v>13</v>
       </c>
       <c r="G135" s="1" t="n">
-        <v>44713</v>
+        <v>44774</v>
       </c>
       <c r="H135" s="1" t="n">
-        <v>44927</v>
+        <v>45017</v>
       </c>
       <c r="I135" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J135" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="136">
@@ -4498,11 +4563,11 @@
         <v>15</v>
       </c>
       <c r="G136" s="1" t="n">
-        <v>45352</v>
+        <v>45839</v>
       </c>
       <c r="H136" s="1"/>
       <c r="I136" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="J136"/>
     </row>
@@ -4558,11 +4623,11 @@
         <v>15</v>
       </c>
       <c r="G138" s="1" t="n">
-        <v>45231</v>
+        <v>45261</v>
       </c>
       <c r="H138" s="1"/>
       <c r="I138" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J138"/>
     </row>
@@ -4589,13 +4654,13 @@
         <v>44927</v>
       </c>
       <c r="H139" s="1" t="n">
-        <v>45689</v>
+        <v>45597</v>
       </c>
       <c r="I139" t="n">
         <v>36</v>
       </c>
       <c r="J139" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="140">
@@ -4615,12 +4680,20 @@
         <v>36</v>
       </c>
       <c r="F140" t="s">
-        <v>20</v>
-      </c>
-      <c r="G140" s="1"/>
-      <c r="H140" s="1"/>
-      <c r="I140"/>
-      <c r="J140"/>
+        <v>13</v>
+      </c>
+      <c r="G140" s="1" t="n">
+        <v>45200</v>
+      </c>
+      <c r="H140" s="1" t="n">
+        <v>45474</v>
+      </c>
+      <c r="I140" t="n">
+        <v>45</v>
+      </c>
+      <c r="J140" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
@@ -4642,13 +4715,13 @@
         <v>13</v>
       </c>
       <c r="G141" s="1" t="n">
-        <v>45078</v>
+        <v>44986</v>
       </c>
       <c r="H141" s="1" t="n">
         <v>45413</v>
       </c>
       <c r="I141" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="J141" t="n">
         <v>52</v>
@@ -4674,13 +4747,13 @@
         <v>13</v>
       </c>
       <c r="G142" s="1" t="n">
-        <v>45139</v>
+        <v>45108</v>
       </c>
       <c r="H142" s="1" t="n">
         <v>45536</v>
       </c>
       <c r="I142" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J142" t="n">
         <v>56</v>
@@ -4709,13 +4782,13 @@
         <v>44927</v>
       </c>
       <c r="H143" s="1" t="n">
-        <v>45383</v>
+        <v>45413</v>
       </c>
       <c r="I143" t="n">
         <v>36</v>
       </c>
       <c r="J143" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="144">
@@ -4769,13 +4842,2173 @@
         <v>44682</v>
       </c>
       <c r="H145" s="1" t="n">
-        <v>44866</v>
+        <v>44896</v>
       </c>
       <c r="I145" t="n">
         <v>28</v>
       </c>
       <c r="J145" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>48</v>
+      </c>
+      <c r="B146" t="n">
+        <v>1</v>
+      </c>
+      <c r="C146" t="n">
+        <v>2</v>
+      </c>
+      <c r="D146" t="s">
+        <v>11</v>
+      </c>
+      <c r="E146" t="s">
+        <v>12</v>
+      </c>
+      <c r="F146" t="s">
+        <v>13</v>
+      </c>
+      <c r="G146" s="1" t="n">
+        <v>44866</v>
+      </c>
+      <c r="H146" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="I146" t="n">
         <v>34</v>
+      </c>
+      <c r="J146" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>48</v>
+      </c>
+      <c r="B147" t="n">
+        <v>1</v>
+      </c>
+      <c r="C147" t="n">
+        <v>2</v>
+      </c>
+      <c r="D147" t="s">
+        <v>14</v>
+      </c>
+      <c r="E147" t="s">
+        <v>12</v>
+      </c>
+      <c r="F147" t="s">
+        <v>15</v>
+      </c>
+      <c r="G147" s="1" t="n">
+        <v>45170</v>
+      </c>
+      <c r="H147" s="1"/>
+      <c r="I147" t="n">
+        <v>44</v>
+      </c>
+      <c r="J147"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>48</v>
+      </c>
+      <c r="B148" t="n">
+        <v>1</v>
+      </c>
+      <c r="C148" t="n">
+        <v>2</v>
+      </c>
+      <c r="D148" t="s">
+        <v>16</v>
+      </c>
+      <c r="E148" t="s">
+        <v>12</v>
+      </c>
+      <c r="F148" t="s">
+        <v>15</v>
+      </c>
+      <c r="G148" s="1" t="n">
+        <v>45505</v>
+      </c>
+      <c r="H148" s="1"/>
+      <c r="I148" t="n">
+        <v>55</v>
+      </c>
+      <c r="J148"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>48</v>
+      </c>
+      <c r="B149" t="n">
+        <v>1</v>
+      </c>
+      <c r="C149" t="n">
+        <v>2</v>
+      </c>
+      <c r="D149" t="s">
+        <v>17</v>
+      </c>
+      <c r="E149" t="s">
+        <v>12</v>
+      </c>
+      <c r="F149" t="s">
+        <v>15</v>
+      </c>
+      <c r="G149" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="H149" s="1"/>
+      <c r="I149" t="n">
+        <v>68</v>
+      </c>
+      <c r="J149"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>48</v>
+      </c>
+      <c r="B150" t="n">
+        <v>1</v>
+      </c>
+      <c r="C150" t="n">
+        <v>2</v>
+      </c>
+      <c r="D150" t="s">
+        <v>18</v>
+      </c>
+      <c r="E150" t="s">
+        <v>12</v>
+      </c>
+      <c r="F150" t="s">
+        <v>15</v>
+      </c>
+      <c r="G150" s="1" t="n">
+        <v>45689</v>
+      </c>
+      <c r="H150" s="1"/>
+      <c r="I150" t="n">
+        <v>61</v>
+      </c>
+      <c r="J150"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>48</v>
+      </c>
+      <c r="B151" t="n">
+        <v>1</v>
+      </c>
+      <c r="C151" t="n">
+        <v>2</v>
+      </c>
+      <c r="D151" t="s">
+        <v>19</v>
+      </c>
+      <c r="E151" t="s">
+        <v>12</v>
+      </c>
+      <c r="F151" t="s">
+        <v>20</v>
+      </c>
+      <c r="G151" s="1"/>
+      <c r="H151" s="1"/>
+      <c r="I151"/>
+      <c r="J151"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>48</v>
+      </c>
+      <c r="B152" t="n">
+        <v>1</v>
+      </c>
+      <c r="C152" t="n">
+        <v>2</v>
+      </c>
+      <c r="D152" t="s">
+        <v>21</v>
+      </c>
+      <c r="E152" t="s">
+        <v>22</v>
+      </c>
+      <c r="F152" t="s">
+        <v>15</v>
+      </c>
+      <c r="G152" s="1" t="n">
+        <v>44896</v>
+      </c>
+      <c r="H152" s="1"/>
+      <c r="I152" t="n">
+        <v>35</v>
+      </c>
+      <c r="J152"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>48</v>
+      </c>
+      <c r="B153" t="n">
+        <v>1</v>
+      </c>
+      <c r="C153" t="n">
+        <v>2</v>
+      </c>
+      <c r="D153" t="s">
+        <v>23</v>
+      </c>
+      <c r="E153" t="s">
+        <v>22</v>
+      </c>
+      <c r="F153" t="s">
+        <v>24</v>
+      </c>
+      <c r="G153" s="1"/>
+      <c r="H153" s="1"/>
+      <c r="I153"/>
+      <c r="J153"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>48</v>
+      </c>
+      <c r="B154" t="n">
+        <v>1</v>
+      </c>
+      <c r="C154" t="n">
+        <v>2</v>
+      </c>
+      <c r="D154" t="s">
+        <v>25</v>
+      </c>
+      <c r="E154" t="s">
+        <v>22</v>
+      </c>
+      <c r="F154" t="s">
+        <v>13</v>
+      </c>
+      <c r="G154" s="1" t="n">
+        <v>44682</v>
+      </c>
+      <c r="H154" s="1" t="n">
+        <v>45352</v>
+      </c>
+      <c r="I154" t="n">
+        <v>28</v>
+      </c>
+      <c r="J154" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>48</v>
+      </c>
+      <c r="B155" t="n">
+        <v>1</v>
+      </c>
+      <c r="C155" t="n">
+        <v>2</v>
+      </c>
+      <c r="D155" t="s">
+        <v>26</v>
+      </c>
+      <c r="E155" t="s">
+        <v>22</v>
+      </c>
+      <c r="F155" t="s">
+        <v>13</v>
+      </c>
+      <c r="G155" s="1" t="n">
+        <v>44166</v>
+      </c>
+      <c r="H155" s="1" t="n">
+        <v>44805</v>
+      </c>
+      <c r="I155" t="n">
+        <v>11</v>
+      </c>
+      <c r="J155" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>48</v>
+      </c>
+      <c r="B156" t="n">
+        <v>1</v>
+      </c>
+      <c r="C156" t="n">
+        <v>2</v>
+      </c>
+      <c r="D156" t="s">
+        <v>27</v>
+      </c>
+      <c r="E156" t="s">
+        <v>22</v>
+      </c>
+      <c r="F156" t="s">
+        <v>13</v>
+      </c>
+      <c r="G156" s="1" t="n">
+        <v>44682</v>
+      </c>
+      <c r="H156" s="1" t="n">
+        <v>44927</v>
+      </c>
+      <c r="I156" t="n">
+        <v>28</v>
+      </c>
+      <c r="J156" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>48</v>
+      </c>
+      <c r="B157" t="n">
+        <v>1</v>
+      </c>
+      <c r="C157" t="n">
+        <v>2</v>
+      </c>
+      <c r="D157" t="s">
+        <v>28</v>
+      </c>
+      <c r="E157" t="s">
+        <v>22</v>
+      </c>
+      <c r="F157" t="s">
+        <v>13</v>
+      </c>
+      <c r="G157" s="1" t="n">
+        <v>43983</v>
+      </c>
+      <c r="H157" s="1" t="n">
+        <v>44044</v>
+      </c>
+      <c r="I157" t="n">
+        <v>5</v>
+      </c>
+      <c r="J157" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>48</v>
+      </c>
+      <c r="B158" t="n">
+        <v>1</v>
+      </c>
+      <c r="C158" t="n">
+        <v>2</v>
+      </c>
+      <c r="D158" t="s">
+        <v>29</v>
+      </c>
+      <c r="E158" t="s">
+        <v>30</v>
+      </c>
+      <c r="F158" t="s">
+        <v>13</v>
+      </c>
+      <c r="G158" s="1" t="n">
+        <v>44105</v>
+      </c>
+      <c r="H158" s="1" t="n">
+        <v>44805</v>
+      </c>
+      <c r="I158" t="n">
+        <v>9</v>
+      </c>
+      <c r="J158" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>48</v>
+      </c>
+      <c r="B159" t="n">
+        <v>1</v>
+      </c>
+      <c r="C159" t="n">
+        <v>2</v>
+      </c>
+      <c r="D159" t="s">
+        <v>31</v>
+      </c>
+      <c r="E159" t="s">
+        <v>30</v>
+      </c>
+      <c r="F159" t="s">
+        <v>13</v>
+      </c>
+      <c r="G159" s="1" t="n">
+        <v>44774</v>
+      </c>
+      <c r="H159" s="1" t="n">
+        <v>45017</v>
+      </c>
+      <c r="I159" t="n">
+        <v>31</v>
+      </c>
+      <c r="J159" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>48</v>
+      </c>
+      <c r="B160" t="n">
+        <v>1</v>
+      </c>
+      <c r="C160" t="n">
+        <v>2</v>
+      </c>
+      <c r="D160" t="s">
+        <v>32</v>
+      </c>
+      <c r="E160" t="s">
+        <v>30</v>
+      </c>
+      <c r="F160" t="s">
+        <v>15</v>
+      </c>
+      <c r="G160" s="1" t="n">
+        <v>44044</v>
+      </c>
+      <c r="H160" s="1"/>
+      <c r="I160" t="n">
+        <v>7</v>
+      </c>
+      <c r="J160"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>48</v>
+      </c>
+      <c r="B161" t="n">
+        <v>1</v>
+      </c>
+      <c r="C161" t="n">
+        <v>2</v>
+      </c>
+      <c r="D161" t="s">
+        <v>33</v>
+      </c>
+      <c r="E161" t="s">
+        <v>30</v>
+      </c>
+      <c r="F161" t="s">
+        <v>13</v>
+      </c>
+      <c r="G161" s="1" t="n">
+        <v>44743</v>
+      </c>
+      <c r="H161" s="1" t="n">
+        <v>45474</v>
+      </c>
+      <c r="I161" t="n">
+        <v>30</v>
+      </c>
+      <c r="J161" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>48</v>
+      </c>
+      <c r="B162" t="n">
+        <v>1</v>
+      </c>
+      <c r="C162" t="n">
+        <v>2</v>
+      </c>
+      <c r="D162" t="s">
+        <v>34</v>
+      </c>
+      <c r="E162" t="s">
+        <v>30</v>
+      </c>
+      <c r="F162" t="s">
+        <v>15</v>
+      </c>
+      <c r="G162" s="1" t="n">
+        <v>45261</v>
+      </c>
+      <c r="H162" s="1"/>
+      <c r="I162" t="n">
+        <v>47</v>
+      </c>
+      <c r="J162"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>48</v>
+      </c>
+      <c r="B163" t="n">
+        <v>1</v>
+      </c>
+      <c r="C163" t="n">
+        <v>2</v>
+      </c>
+      <c r="D163" t="s">
+        <v>35</v>
+      </c>
+      <c r="E163" t="s">
+        <v>36</v>
+      </c>
+      <c r="F163" t="s">
+        <v>13</v>
+      </c>
+      <c r="G163" s="1" t="n">
+        <v>44927</v>
+      </c>
+      <c r="H163" s="1" t="n">
+        <v>45597</v>
+      </c>
+      <c r="I163" t="n">
+        <v>36</v>
+      </c>
+      <c r="J163" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>48</v>
+      </c>
+      <c r="B164" t="n">
+        <v>1</v>
+      </c>
+      <c r="C164" t="n">
+        <v>2</v>
+      </c>
+      <c r="D164" t="s">
+        <v>37</v>
+      </c>
+      <c r="E164" t="s">
+        <v>36</v>
+      </c>
+      <c r="F164" t="s">
+        <v>13</v>
+      </c>
+      <c r="G164" s="1" t="n">
+        <v>44774</v>
+      </c>
+      <c r="H164" s="1" t="n">
+        <v>45474</v>
+      </c>
+      <c r="I164" t="n">
+        <v>31</v>
+      </c>
+      <c r="J164" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>48</v>
+      </c>
+      <c r="B165" t="n">
+        <v>1</v>
+      </c>
+      <c r="C165" t="n">
+        <v>2</v>
+      </c>
+      <c r="D165" t="s">
+        <v>38</v>
+      </c>
+      <c r="E165" t="s">
+        <v>36</v>
+      </c>
+      <c r="F165" t="s">
+        <v>13</v>
+      </c>
+      <c r="G165" s="1" t="n">
+        <v>44986</v>
+      </c>
+      <c r="H165" s="1" t="n">
+        <v>45413</v>
+      </c>
+      <c r="I165" t="n">
+        <v>38</v>
+      </c>
+      <c r="J165" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>48</v>
+      </c>
+      <c r="B166" t="n">
+        <v>1</v>
+      </c>
+      <c r="C166" t="n">
+        <v>2</v>
+      </c>
+      <c r="D166" t="s">
+        <v>39</v>
+      </c>
+      <c r="E166" t="s">
+        <v>36</v>
+      </c>
+      <c r="F166" t="s">
+        <v>13</v>
+      </c>
+      <c r="G166" s="1" t="n">
+        <v>45108</v>
+      </c>
+      <c r="H166" s="1" t="n">
+        <v>45536</v>
+      </c>
+      <c r="I166" t="n">
+        <v>42</v>
+      </c>
+      <c r="J166" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>48</v>
+      </c>
+      <c r="B167" t="n">
+        <v>1</v>
+      </c>
+      <c r="C167" t="n">
+        <v>2</v>
+      </c>
+      <c r="D167" t="s">
+        <v>40</v>
+      </c>
+      <c r="E167" t="s">
+        <v>36</v>
+      </c>
+      <c r="F167" t="s">
+        <v>13</v>
+      </c>
+      <c r="G167" s="1" t="n">
+        <v>44927</v>
+      </c>
+      <c r="H167" s="1" t="n">
+        <v>45413</v>
+      </c>
+      <c r="I167" t="n">
+        <v>36</v>
+      </c>
+      <c r="J167" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>48</v>
+      </c>
+      <c r="B168" t="n">
+        <v>1</v>
+      </c>
+      <c r="C168" t="n">
+        <v>2</v>
+      </c>
+      <c r="D168" t="s">
+        <v>41</v>
+      </c>
+      <c r="E168" t="s">
+        <v>36</v>
+      </c>
+      <c r="F168" t="s">
+        <v>15</v>
+      </c>
+      <c r="G168" s="1" t="n">
+        <v>44105</v>
+      </c>
+      <c r="H168" s="1"/>
+      <c r="I168" t="n">
+        <v>9</v>
+      </c>
+      <c r="J168"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>48</v>
+      </c>
+      <c r="B169" t="n">
+        <v>1</v>
+      </c>
+      <c r="C169" t="n">
+        <v>2</v>
+      </c>
+      <c r="D169" t="s">
+        <v>42</v>
+      </c>
+      <c r="E169" t="s">
+        <v>36</v>
+      </c>
+      <c r="F169" t="s">
+        <v>13</v>
+      </c>
+      <c r="G169" s="1" t="n">
+        <v>44378</v>
+      </c>
+      <c r="H169" s="1" t="n">
+        <v>44896</v>
+      </c>
+      <c r="I169" t="n">
+        <v>18</v>
+      </c>
+      <c r="J169" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>49</v>
+      </c>
+      <c r="B170" t="n">
+        <v>1</v>
+      </c>
+      <c r="C170" t="n">
+        <v>3</v>
+      </c>
+      <c r="D170" t="s">
+        <v>11</v>
+      </c>
+      <c r="E170" t="s">
+        <v>12</v>
+      </c>
+      <c r="F170" t="s">
+        <v>13</v>
+      </c>
+      <c r="G170" s="1" t="n">
+        <v>44866</v>
+      </c>
+      <c r="H170" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="I170" t="n">
+        <v>34</v>
+      </c>
+      <c r="J170" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>49</v>
+      </c>
+      <c r="B171" t="n">
+        <v>1</v>
+      </c>
+      <c r="C171" t="n">
+        <v>3</v>
+      </c>
+      <c r="D171" t="s">
+        <v>14</v>
+      </c>
+      <c r="E171" t="s">
+        <v>12</v>
+      </c>
+      <c r="F171" t="s">
+        <v>15</v>
+      </c>
+      <c r="G171" s="1" t="n">
+        <v>45170</v>
+      </c>
+      <c r="H171" s="1"/>
+      <c r="I171" t="n">
+        <v>44</v>
+      </c>
+      <c r="J171"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>49</v>
+      </c>
+      <c r="B172" t="n">
+        <v>1</v>
+      </c>
+      <c r="C172" t="n">
+        <v>3</v>
+      </c>
+      <c r="D172" t="s">
+        <v>16</v>
+      </c>
+      <c r="E172" t="s">
+        <v>12</v>
+      </c>
+      <c r="F172" t="s">
+        <v>15</v>
+      </c>
+      <c r="G172" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="H172" s="1"/>
+      <c r="I172" t="n">
+        <v>66</v>
+      </c>
+      <c r="J172"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>49</v>
+      </c>
+      <c r="B173" t="n">
+        <v>1</v>
+      </c>
+      <c r="C173" t="n">
+        <v>3</v>
+      </c>
+      <c r="D173" t="s">
+        <v>17</v>
+      </c>
+      <c r="E173" t="s">
+        <v>12</v>
+      </c>
+      <c r="F173" t="s">
+        <v>15</v>
+      </c>
+      <c r="G173" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="H173" s="1"/>
+      <c r="I173" t="n">
+        <v>68</v>
+      </c>
+      <c r="J173"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>49</v>
+      </c>
+      <c r="B174" t="n">
+        <v>1</v>
+      </c>
+      <c r="C174" t="n">
+        <v>3</v>
+      </c>
+      <c r="D174" t="s">
+        <v>18</v>
+      </c>
+      <c r="E174" t="s">
+        <v>12</v>
+      </c>
+      <c r="F174" t="s">
+        <v>15</v>
+      </c>
+      <c r="G174" s="1" t="n">
+        <v>45689</v>
+      </c>
+      <c r="H174" s="1"/>
+      <c r="I174" t="n">
+        <v>61</v>
+      </c>
+      <c r="J174"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>49</v>
+      </c>
+      <c r="B175" t="n">
+        <v>1</v>
+      </c>
+      <c r="C175" t="n">
+        <v>3</v>
+      </c>
+      <c r="D175" t="s">
+        <v>19</v>
+      </c>
+      <c r="E175" t="s">
+        <v>12</v>
+      </c>
+      <c r="F175" t="s">
+        <v>20</v>
+      </c>
+      <c r="G175" s="1"/>
+      <c r="H175" s="1"/>
+      <c r="I175"/>
+      <c r="J175"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>49</v>
+      </c>
+      <c r="B176" t="n">
+        <v>1</v>
+      </c>
+      <c r="C176" t="n">
+        <v>3</v>
+      </c>
+      <c r="D176" t="s">
+        <v>21</v>
+      </c>
+      <c r="E176" t="s">
+        <v>22</v>
+      </c>
+      <c r="F176" t="s">
+        <v>15</v>
+      </c>
+      <c r="G176" s="1" t="n">
+        <v>44896</v>
+      </c>
+      <c r="H176" s="1"/>
+      <c r="I176" t="n">
+        <v>35</v>
+      </c>
+      <c r="J176"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>49</v>
+      </c>
+      <c r="B177" t="n">
+        <v>1</v>
+      </c>
+      <c r="C177" t="n">
+        <v>3</v>
+      </c>
+      <c r="D177" t="s">
+        <v>23</v>
+      </c>
+      <c r="E177" t="s">
+        <v>22</v>
+      </c>
+      <c r="F177" t="s">
+        <v>24</v>
+      </c>
+      <c r="G177" s="1"/>
+      <c r="H177" s="1"/>
+      <c r="I177"/>
+      <c r="J177"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>49</v>
+      </c>
+      <c r="B178" t="n">
+        <v>1</v>
+      </c>
+      <c r="C178" t="n">
+        <v>3</v>
+      </c>
+      <c r="D178" t="s">
+        <v>25</v>
+      </c>
+      <c r="E178" t="s">
+        <v>22</v>
+      </c>
+      <c r="F178" t="s">
+        <v>13</v>
+      </c>
+      <c r="G178" s="1" t="n">
+        <v>44682</v>
+      </c>
+      <c r="H178" s="1" t="n">
+        <v>45352</v>
+      </c>
+      <c r="I178" t="n">
+        <v>28</v>
+      </c>
+      <c r="J178" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>49</v>
+      </c>
+      <c r="B179" t="n">
+        <v>1</v>
+      </c>
+      <c r="C179" t="n">
+        <v>3</v>
+      </c>
+      <c r="D179" t="s">
+        <v>26</v>
+      </c>
+      <c r="E179" t="s">
+        <v>22</v>
+      </c>
+      <c r="F179" t="s">
+        <v>13</v>
+      </c>
+      <c r="G179" s="1" t="n">
+        <v>44166</v>
+      </c>
+      <c r="H179" s="1" t="n">
+        <v>44805</v>
+      </c>
+      <c r="I179" t="n">
+        <v>11</v>
+      </c>
+      <c r="J179" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>49</v>
+      </c>
+      <c r="B180" t="n">
+        <v>1</v>
+      </c>
+      <c r="C180" t="n">
+        <v>3</v>
+      </c>
+      <c r="D180" t="s">
+        <v>27</v>
+      </c>
+      <c r="E180" t="s">
+        <v>22</v>
+      </c>
+      <c r="F180" t="s">
+        <v>13</v>
+      </c>
+      <c r="G180" s="1" t="n">
+        <v>44682</v>
+      </c>
+      <c r="H180" s="1" t="n">
+        <v>44927</v>
+      </c>
+      <c r="I180" t="n">
+        <v>28</v>
+      </c>
+      <c r="J180" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>49</v>
+      </c>
+      <c r="B181" t="n">
+        <v>1</v>
+      </c>
+      <c r="C181" t="n">
+        <v>3</v>
+      </c>
+      <c r="D181" t="s">
+        <v>28</v>
+      </c>
+      <c r="E181" t="s">
+        <v>22</v>
+      </c>
+      <c r="F181" t="s">
+        <v>13</v>
+      </c>
+      <c r="G181" s="1" t="n">
+        <v>43983</v>
+      </c>
+      <c r="H181" s="1" t="n">
+        <v>44044</v>
+      </c>
+      <c r="I181" t="n">
+        <v>5</v>
+      </c>
+      <c r="J181" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>49</v>
+      </c>
+      <c r="B182" t="n">
+        <v>1</v>
+      </c>
+      <c r="C182" t="n">
+        <v>3</v>
+      </c>
+      <c r="D182" t="s">
+        <v>29</v>
+      </c>
+      <c r="E182" t="s">
+        <v>30</v>
+      </c>
+      <c r="F182" t="s">
+        <v>13</v>
+      </c>
+      <c r="G182" s="1" t="n">
+        <v>44105</v>
+      </c>
+      <c r="H182" s="1" t="n">
+        <v>44805</v>
+      </c>
+      <c r="I182" t="n">
+        <v>9</v>
+      </c>
+      <c r="J182" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>49</v>
+      </c>
+      <c r="B183" t="n">
+        <v>1</v>
+      </c>
+      <c r="C183" t="n">
+        <v>3</v>
+      </c>
+      <c r="D183" t="s">
+        <v>31</v>
+      </c>
+      <c r="E183" t="s">
+        <v>30</v>
+      </c>
+      <c r="F183" t="s">
+        <v>13</v>
+      </c>
+      <c r="G183" s="1" t="n">
+        <v>44774</v>
+      </c>
+      <c r="H183" s="1" t="n">
+        <v>45017</v>
+      </c>
+      <c r="I183" t="n">
+        <v>31</v>
+      </c>
+      <c r="J183" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>49</v>
+      </c>
+      <c r="B184" t="n">
+        <v>1</v>
+      </c>
+      <c r="C184" t="n">
+        <v>3</v>
+      </c>
+      <c r="D184" t="s">
+        <v>32</v>
+      </c>
+      <c r="E184" t="s">
+        <v>30</v>
+      </c>
+      <c r="F184" t="s">
+        <v>15</v>
+      </c>
+      <c r="G184" s="1" t="n">
+        <v>44774</v>
+      </c>
+      <c r="H184" s="1"/>
+      <c r="I184" t="n">
+        <v>31</v>
+      </c>
+      <c r="J184"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>49</v>
+      </c>
+      <c r="B185" t="n">
+        <v>1</v>
+      </c>
+      <c r="C185" t="n">
+        <v>3</v>
+      </c>
+      <c r="D185" t="s">
+        <v>33</v>
+      </c>
+      <c r="E185" t="s">
+        <v>30</v>
+      </c>
+      <c r="F185" t="s">
+        <v>13</v>
+      </c>
+      <c r="G185" s="1" t="n">
+        <v>44743</v>
+      </c>
+      <c r="H185" s="1" t="n">
+        <v>45474</v>
+      </c>
+      <c r="I185" t="n">
+        <v>30</v>
+      </c>
+      <c r="J185" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>49</v>
+      </c>
+      <c r="B186" t="n">
+        <v>1</v>
+      </c>
+      <c r="C186" t="n">
+        <v>3</v>
+      </c>
+      <c r="D186" t="s">
+        <v>34</v>
+      </c>
+      <c r="E186" t="s">
+        <v>30</v>
+      </c>
+      <c r="F186" t="s">
+        <v>15</v>
+      </c>
+      <c r="G186" s="1" t="n">
+        <v>45261</v>
+      </c>
+      <c r="H186" s="1"/>
+      <c r="I186" t="n">
+        <v>47</v>
+      </c>
+      <c r="J186"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>49</v>
+      </c>
+      <c r="B187" t="n">
+        <v>1</v>
+      </c>
+      <c r="C187" t="n">
+        <v>3</v>
+      </c>
+      <c r="D187" t="s">
+        <v>35</v>
+      </c>
+      <c r="E187" t="s">
+        <v>36</v>
+      </c>
+      <c r="F187" t="s">
+        <v>13</v>
+      </c>
+      <c r="G187" s="1" t="n">
+        <v>44927</v>
+      </c>
+      <c r="H187" s="1" t="n">
+        <v>45597</v>
+      </c>
+      <c r="I187" t="n">
+        <v>36</v>
+      </c>
+      <c r="J187" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>49</v>
+      </c>
+      <c r="B188" t="n">
+        <v>1</v>
+      </c>
+      <c r="C188" t="n">
+        <v>3</v>
+      </c>
+      <c r="D188" t="s">
+        <v>37</v>
+      </c>
+      <c r="E188" t="s">
+        <v>36</v>
+      </c>
+      <c r="F188" t="s">
+        <v>13</v>
+      </c>
+      <c r="G188" s="1" t="n">
+        <v>44927</v>
+      </c>
+      <c r="H188" s="1" t="n">
+        <v>45474</v>
+      </c>
+      <c r="I188" t="n">
+        <v>36</v>
+      </c>
+      <c r="J188" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>49</v>
+      </c>
+      <c r="B189" t="n">
+        <v>1</v>
+      </c>
+      <c r="C189" t="n">
+        <v>3</v>
+      </c>
+      <c r="D189" t="s">
+        <v>38</v>
+      </c>
+      <c r="E189" t="s">
+        <v>36</v>
+      </c>
+      <c r="F189" t="s">
+        <v>13</v>
+      </c>
+      <c r="G189" s="1" t="n">
+        <v>44986</v>
+      </c>
+      <c r="H189" s="1" t="n">
+        <v>45413</v>
+      </c>
+      <c r="I189" t="n">
+        <v>38</v>
+      </c>
+      <c r="J189" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>49</v>
+      </c>
+      <c r="B190" t="n">
+        <v>1</v>
+      </c>
+      <c r="C190" t="n">
+        <v>3</v>
+      </c>
+      <c r="D190" t="s">
+        <v>39</v>
+      </c>
+      <c r="E190" t="s">
+        <v>36</v>
+      </c>
+      <c r="F190" t="s">
+        <v>13</v>
+      </c>
+      <c r="G190" s="1" t="n">
+        <v>45108</v>
+      </c>
+      <c r="H190" s="1" t="n">
+        <v>45536</v>
+      </c>
+      <c r="I190" t="n">
+        <v>42</v>
+      </c>
+      <c r="J190" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>49</v>
+      </c>
+      <c r="B191" t="n">
+        <v>1</v>
+      </c>
+      <c r="C191" t="n">
+        <v>3</v>
+      </c>
+      <c r="D191" t="s">
+        <v>40</v>
+      </c>
+      <c r="E191" t="s">
+        <v>36</v>
+      </c>
+      <c r="F191" t="s">
+        <v>13</v>
+      </c>
+      <c r="G191" s="1" t="n">
+        <v>44927</v>
+      </c>
+      <c r="H191" s="1" t="n">
+        <v>45413</v>
+      </c>
+      <c r="I191" t="n">
+        <v>36</v>
+      </c>
+      <c r="J191" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>49</v>
+      </c>
+      <c r="B192" t="n">
+        <v>1</v>
+      </c>
+      <c r="C192" t="n">
+        <v>3</v>
+      </c>
+      <c r="D192" t="s">
+        <v>41</v>
+      </c>
+      <c r="E192" t="s">
+        <v>36</v>
+      </c>
+      <c r="F192" t="s">
+        <v>15</v>
+      </c>
+      <c r="G192" s="1" t="n">
+        <v>45292</v>
+      </c>
+      <c r="H192" s="1"/>
+      <c r="I192" t="n">
+        <v>48</v>
+      </c>
+      <c r="J192"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>49</v>
+      </c>
+      <c r="B193" t="n">
+        <v>1</v>
+      </c>
+      <c r="C193" t="n">
+        <v>3</v>
+      </c>
+      <c r="D193" t="s">
+        <v>42</v>
+      </c>
+      <c r="E193" t="s">
+        <v>36</v>
+      </c>
+      <c r="F193" t="s">
+        <v>13</v>
+      </c>
+      <c r="G193" s="1" t="n">
+        <v>44682</v>
+      </c>
+      <c r="H193" s="1" t="n">
+        <v>44896</v>
+      </c>
+      <c r="I193" t="n">
+        <v>28</v>
+      </c>
+      <c r="J193" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>50</v>
+      </c>
+      <c r="B194" t="n">
+        <v>1</v>
+      </c>
+      <c r="C194" t="n">
+        <v>4</v>
+      </c>
+      <c r="D194" t="s">
+        <v>11</v>
+      </c>
+      <c r="E194" t="s">
+        <v>12</v>
+      </c>
+      <c r="F194" t="s">
+        <v>13</v>
+      </c>
+      <c r="G194" s="1" t="n">
+        <v>44866</v>
+      </c>
+      <c r="H194" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="I194" t="n">
+        <v>34</v>
+      </c>
+      <c r="J194" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>50</v>
+      </c>
+      <c r="B195" t="n">
+        <v>1</v>
+      </c>
+      <c r="C195" t="n">
+        <v>4</v>
+      </c>
+      <c r="D195" t="s">
+        <v>14</v>
+      </c>
+      <c r="E195" t="s">
+        <v>12</v>
+      </c>
+      <c r="F195" t="s">
+        <v>15</v>
+      </c>
+      <c r="G195" s="1" t="n">
+        <v>45170</v>
+      </c>
+      <c r="H195" s="1"/>
+      <c r="I195" t="n">
+        <v>44</v>
+      </c>
+      <c r="J195"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>50</v>
+      </c>
+      <c r="B196" t="n">
+        <v>1</v>
+      </c>
+      <c r="C196" t="n">
+        <v>4</v>
+      </c>
+      <c r="D196" t="s">
+        <v>16</v>
+      </c>
+      <c r="E196" t="s">
+        <v>12</v>
+      </c>
+      <c r="F196" t="s">
+        <v>15</v>
+      </c>
+      <c r="G196" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="H196" s="1"/>
+      <c r="I196" t="n">
+        <v>66</v>
+      </c>
+      <c r="J196"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>50</v>
+      </c>
+      <c r="B197" t="n">
+        <v>1</v>
+      </c>
+      <c r="C197" t="n">
+        <v>4</v>
+      </c>
+      <c r="D197" t="s">
+        <v>17</v>
+      </c>
+      <c r="E197" t="s">
+        <v>12</v>
+      </c>
+      <c r="F197" t="s">
+        <v>15</v>
+      </c>
+      <c r="G197" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="H197" s="1"/>
+      <c r="I197" t="n">
+        <v>68</v>
+      </c>
+      <c r="J197"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>50</v>
+      </c>
+      <c r="B198" t="n">
+        <v>1</v>
+      </c>
+      <c r="C198" t="n">
+        <v>4</v>
+      </c>
+      <c r="D198" t="s">
+        <v>18</v>
+      </c>
+      <c r="E198" t="s">
+        <v>12</v>
+      </c>
+      <c r="F198" t="s">
+        <v>15</v>
+      </c>
+      <c r="G198" s="1" t="n">
+        <v>45689</v>
+      </c>
+      <c r="H198" s="1"/>
+      <c r="I198" t="n">
+        <v>61</v>
+      </c>
+      <c r="J198"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>50</v>
+      </c>
+      <c r="B199" t="n">
+        <v>1</v>
+      </c>
+      <c r="C199" t="n">
+        <v>4</v>
+      </c>
+      <c r="D199" t="s">
+        <v>19</v>
+      </c>
+      <c r="E199" t="s">
+        <v>12</v>
+      </c>
+      <c r="F199" t="s">
+        <v>20</v>
+      </c>
+      <c r="G199" s="1"/>
+      <c r="H199" s="1"/>
+      <c r="I199"/>
+      <c r="J199"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>50</v>
+      </c>
+      <c r="B200" t="n">
+        <v>1</v>
+      </c>
+      <c r="C200" t="n">
+        <v>4</v>
+      </c>
+      <c r="D200" t="s">
+        <v>21</v>
+      </c>
+      <c r="E200" t="s">
+        <v>22</v>
+      </c>
+      <c r="F200" t="s">
+        <v>15</v>
+      </c>
+      <c r="G200" s="1" t="n">
+        <v>44896</v>
+      </c>
+      <c r="H200" s="1"/>
+      <c r="I200" t="n">
+        <v>35</v>
+      </c>
+      <c r="J200"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>50</v>
+      </c>
+      <c r="B201" t="n">
+        <v>1</v>
+      </c>
+      <c r="C201" t="n">
+        <v>4</v>
+      </c>
+      <c r="D201" t="s">
+        <v>23</v>
+      </c>
+      <c r="E201" t="s">
+        <v>22</v>
+      </c>
+      <c r="F201" t="s">
+        <v>24</v>
+      </c>
+      <c r="G201" s="1"/>
+      <c r="H201" s="1"/>
+      <c r="I201"/>
+      <c r="J201"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="s">
+        <v>50</v>
+      </c>
+      <c r="B202" t="n">
+        <v>1</v>
+      </c>
+      <c r="C202" t="n">
+        <v>4</v>
+      </c>
+      <c r="D202" t="s">
+        <v>25</v>
+      </c>
+      <c r="E202" t="s">
+        <v>22</v>
+      </c>
+      <c r="F202" t="s">
+        <v>13</v>
+      </c>
+      <c r="G202" s="1" t="n">
+        <v>44682</v>
+      </c>
+      <c r="H202" s="1" t="n">
+        <v>45352</v>
+      </c>
+      <c r="I202" t="n">
+        <v>28</v>
+      </c>
+      <c r="J202" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="s">
+        <v>50</v>
+      </c>
+      <c r="B203" t="n">
+        <v>1</v>
+      </c>
+      <c r="C203" t="n">
+        <v>4</v>
+      </c>
+      <c r="D203" t="s">
+        <v>26</v>
+      </c>
+      <c r="E203" t="s">
+        <v>22</v>
+      </c>
+      <c r="F203" t="s">
+        <v>13</v>
+      </c>
+      <c r="G203" s="1" t="n">
+        <v>44652</v>
+      </c>
+      <c r="H203" s="1" t="n">
+        <v>44805</v>
+      </c>
+      <c r="I203" t="n">
+        <v>27</v>
+      </c>
+      <c r="J203" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="s">
+        <v>50</v>
+      </c>
+      <c r="B204" t="n">
+        <v>1</v>
+      </c>
+      <c r="C204" t="n">
+        <v>4</v>
+      </c>
+      <c r="D204" t="s">
+        <v>27</v>
+      </c>
+      <c r="E204" t="s">
+        <v>22</v>
+      </c>
+      <c r="F204" t="s">
+        <v>13</v>
+      </c>
+      <c r="G204" s="1" t="n">
+        <v>44682</v>
+      </c>
+      <c r="H204" s="1" t="n">
+        <v>44927</v>
+      </c>
+      <c r="I204" t="n">
+        <v>28</v>
+      </c>
+      <c r="J204" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="s">
+        <v>50</v>
+      </c>
+      <c r="B205" t="n">
+        <v>1</v>
+      </c>
+      <c r="C205" t="n">
+        <v>4</v>
+      </c>
+      <c r="D205" t="s">
+        <v>28</v>
+      </c>
+      <c r="E205" t="s">
+        <v>22</v>
+      </c>
+      <c r="F205" t="s">
+        <v>13</v>
+      </c>
+      <c r="G205" s="1" t="n">
+        <v>43983</v>
+      </c>
+      <c r="H205" s="1" t="n">
+        <v>44044</v>
+      </c>
+      <c r="I205" t="n">
+        <v>5</v>
+      </c>
+      <c r="J205" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="s">
+        <v>50</v>
+      </c>
+      <c r="B206" t="n">
+        <v>1</v>
+      </c>
+      <c r="C206" t="n">
+        <v>4</v>
+      </c>
+      <c r="D206" t="s">
+        <v>29</v>
+      </c>
+      <c r="E206" t="s">
+        <v>30</v>
+      </c>
+      <c r="F206" t="s">
+        <v>13</v>
+      </c>
+      <c r="G206" s="1" t="n">
+        <v>44105</v>
+      </c>
+      <c r="H206" s="1" t="n">
+        <v>44805</v>
+      </c>
+      <c r="I206" t="n">
+        <v>9</v>
+      </c>
+      <c r="J206" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="s">
+        <v>50</v>
+      </c>
+      <c r="B207" t="n">
+        <v>1</v>
+      </c>
+      <c r="C207" t="n">
+        <v>4</v>
+      </c>
+      <c r="D207" t="s">
+        <v>31</v>
+      </c>
+      <c r="E207" t="s">
+        <v>30</v>
+      </c>
+      <c r="F207" t="s">
+        <v>13</v>
+      </c>
+      <c r="G207" s="1" t="n">
+        <v>44774</v>
+      </c>
+      <c r="H207" s="1" t="n">
+        <v>45017</v>
+      </c>
+      <c r="I207" t="n">
+        <v>31</v>
+      </c>
+      <c r="J207" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="s">
+        <v>50</v>
+      </c>
+      <c r="B208" t="n">
+        <v>1</v>
+      </c>
+      <c r="C208" t="n">
+        <v>4</v>
+      </c>
+      <c r="D208" t="s">
+        <v>32</v>
+      </c>
+      <c r="E208" t="s">
+        <v>30</v>
+      </c>
+      <c r="F208" t="s">
+        <v>15</v>
+      </c>
+      <c r="G208" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="H208" s="1"/>
+      <c r="I208" t="n">
+        <v>66</v>
+      </c>
+      <c r="J208"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="s">
+        <v>50</v>
+      </c>
+      <c r="B209" t="n">
+        <v>1</v>
+      </c>
+      <c r="C209" t="n">
+        <v>4</v>
+      </c>
+      <c r="D209" t="s">
+        <v>33</v>
+      </c>
+      <c r="E209" t="s">
+        <v>30</v>
+      </c>
+      <c r="F209" t="s">
+        <v>13</v>
+      </c>
+      <c r="G209" s="1" t="n">
+        <v>44743</v>
+      </c>
+      <c r="H209" s="1" t="n">
+        <v>45474</v>
+      </c>
+      <c r="I209" t="n">
+        <v>30</v>
+      </c>
+      <c r="J209" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="s">
+        <v>50</v>
+      </c>
+      <c r="B210" t="n">
+        <v>1</v>
+      </c>
+      <c r="C210" t="n">
+        <v>4</v>
+      </c>
+      <c r="D210" t="s">
+        <v>34</v>
+      </c>
+      <c r="E210" t="s">
+        <v>30</v>
+      </c>
+      <c r="F210" t="s">
+        <v>15</v>
+      </c>
+      <c r="G210" s="1" t="n">
+        <v>45261</v>
+      </c>
+      <c r="H210" s="1"/>
+      <c r="I210" t="n">
+        <v>47</v>
+      </c>
+      <c r="J210"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="s">
+        <v>50</v>
+      </c>
+      <c r="B211" t="n">
+        <v>1</v>
+      </c>
+      <c r="C211" t="n">
+        <v>4</v>
+      </c>
+      <c r="D211" t="s">
+        <v>35</v>
+      </c>
+      <c r="E211" t="s">
+        <v>36</v>
+      </c>
+      <c r="F211" t="s">
+        <v>13</v>
+      </c>
+      <c r="G211" s="1" t="n">
+        <v>44927</v>
+      </c>
+      <c r="H211" s="1" t="n">
+        <v>45597</v>
+      </c>
+      <c r="I211" t="n">
+        <v>36</v>
+      </c>
+      <c r="J211" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="s">
+        <v>50</v>
+      </c>
+      <c r="B212" t="n">
+        <v>1</v>
+      </c>
+      <c r="C212" t="n">
+        <v>4</v>
+      </c>
+      <c r="D212" t="s">
+        <v>37</v>
+      </c>
+      <c r="E212" t="s">
+        <v>36</v>
+      </c>
+      <c r="F212" t="s">
+        <v>13</v>
+      </c>
+      <c r="G212" s="1" t="n">
+        <v>45200</v>
+      </c>
+      <c r="H212" s="1" t="n">
+        <v>45474</v>
+      </c>
+      <c r="I212" t="n">
+        <v>45</v>
+      </c>
+      <c r="J212" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="s">
+        <v>50</v>
+      </c>
+      <c r="B213" t="n">
+        <v>1</v>
+      </c>
+      <c r="C213" t="n">
+        <v>4</v>
+      </c>
+      <c r="D213" t="s">
+        <v>38</v>
+      </c>
+      <c r="E213" t="s">
+        <v>36</v>
+      </c>
+      <c r="F213" t="s">
+        <v>13</v>
+      </c>
+      <c r="G213" s="1" t="n">
+        <v>44986</v>
+      </c>
+      <c r="H213" s="1" t="n">
+        <v>45413</v>
+      </c>
+      <c r="I213" t="n">
+        <v>38</v>
+      </c>
+      <c r="J213" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="s">
+        <v>50</v>
+      </c>
+      <c r="B214" t="n">
+        <v>1</v>
+      </c>
+      <c r="C214" t="n">
+        <v>4</v>
+      </c>
+      <c r="D214" t="s">
+        <v>39</v>
+      </c>
+      <c r="E214" t="s">
+        <v>36</v>
+      </c>
+      <c r="F214" t="s">
+        <v>13</v>
+      </c>
+      <c r="G214" s="1" t="n">
+        <v>45108</v>
+      </c>
+      <c r="H214" s="1" t="n">
+        <v>45536</v>
+      </c>
+      <c r="I214" t="n">
+        <v>42</v>
+      </c>
+      <c r="J214" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="s">
+        <v>50</v>
+      </c>
+      <c r="B215" t="n">
+        <v>1</v>
+      </c>
+      <c r="C215" t="n">
+        <v>4</v>
+      </c>
+      <c r="D215" t="s">
+        <v>40</v>
+      </c>
+      <c r="E215" t="s">
+        <v>36</v>
+      </c>
+      <c r="F215" t="s">
+        <v>13</v>
+      </c>
+      <c r="G215" s="1" t="n">
+        <v>44927</v>
+      </c>
+      <c r="H215" s="1" t="n">
+        <v>45413</v>
+      </c>
+      <c r="I215" t="n">
+        <v>36</v>
+      </c>
+      <c r="J215" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="s">
+        <v>50</v>
+      </c>
+      <c r="B216" t="n">
+        <v>1</v>
+      </c>
+      <c r="C216" t="n">
+        <v>4</v>
+      </c>
+      <c r="D216" t="s">
+        <v>41</v>
+      </c>
+      <c r="E216" t="s">
+        <v>36</v>
+      </c>
+      <c r="F216" t="s">
+        <v>15</v>
+      </c>
+      <c r="G216" s="1" t="n">
+        <v>45292</v>
+      </c>
+      <c r="H216" s="1"/>
+      <c r="I216" t="n">
+        <v>48</v>
+      </c>
+      <c r="J216"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="s">
+        <v>50</v>
+      </c>
+      <c r="B217" t="n">
+        <v>1</v>
+      </c>
+      <c r="C217" t="n">
+        <v>4</v>
+      </c>
+      <c r="D217" t="s">
+        <v>42</v>
+      </c>
+      <c r="E217" t="s">
+        <v>36</v>
+      </c>
+      <c r="F217" t="s">
+        <v>13</v>
+      </c>
+      <c r="G217" s="1" t="n">
+        <v>44682</v>
+      </c>
+      <c r="H217" s="1" t="n">
+        <v>44896</v>
+      </c>
+      <c r="I217" t="n">
+        <v>28</v>
+      </c>
+      <c r="J217" t="n">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
